--- a/artfynd/A 40629-2026 artfynd.xlsx
+++ b/artfynd/A 40629-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ4"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,7 +683,7 @@
         <v>137054854</v>
       </c>
       <c r="B2" t="n">
-        <v>96573</v>
+        <v>96574</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137058376</v>
       </c>
       <c r="B3" t="n">
-        <v>92795</v>
+        <v>92796</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1016,6 +1016,127 @@
       <c r="AZ4" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/137054794</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>137095159</v>
+      </c>
+      <c r="B5" t="n">
+        <v>56739</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>206046</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Älg</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Alces alces</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Kungagraven, Vg</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>337416</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6434858</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>09:56</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>09:56</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Mats Eriksson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Mats Eriksson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137095159</t>
         </is>
       </c>
     </row>
@@ -1024,6 +1145,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 40629-2026 artfynd.xlsx
+++ b/artfynd/A 40629-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137054854</v>
       </c>
       <c r="B2" t="n">
-        <v>96574</v>
+        <v>96580</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137058376</v>
       </c>
       <c r="B3" t="n">
-        <v>92796</v>
+        <v>92802</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 40629-2026 artfynd.xlsx
+++ b/artfynd/A 40629-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137054854</v>
       </c>
       <c r="B2" t="n">
-        <v>96580</v>
+        <v>96584</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137058376</v>
       </c>
       <c r="B3" t="n">
-        <v>92802</v>
+        <v>92806</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 40629-2026 artfynd.xlsx
+++ b/artfynd/A 40629-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ5"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>137054854</v>
+        <v>137168521</v>
       </c>
       <c r="B2" t="n">
-        <v>96584</v>
+        <v>96957</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2812</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kransmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hylocomiadelphus triquetrus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Ochyra &amp; Stebel</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Rapungaberget, Rapungaberget, Vg</t>
+          <t>Kungagraven, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>337503</v>
+        <v>337545</v>
       </c>
       <c r="R2" t="n">
-        <v>6434789</v>
+        <v>6434847</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +745,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,16 +786,16 @@
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137054854</t>
+          <t>https://artportalen.se/Sighting/137168521</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>137058376</v>
+        <v>137054854</v>
       </c>
       <c r="B3" t="n">
-        <v>92806</v>
+        <v>96584</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6031</v>
+        <v>2812</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -833,7 +833,7 @@
         <v>6434789</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -898,38 +898,38 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137058376</t>
+          <t>https://artportalen.se/Sighting/137054854</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>137054794</v>
+        <v>137058376</v>
       </c>
       <c r="B4" t="n">
-        <v>58021</v>
+        <v>92806</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100048</v>
+        <v>6031</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,12 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:55</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Födosökande på grenar av äldre gran</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1015,16 +1010,16 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137054794</t>
+          <t>https://artportalen.se/Sighting/137058376</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>137095159</v>
+        <v>137054794</v>
       </c>
       <c r="B5" t="n">
-        <v>56739</v>
+        <v>58021</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1032,16 +1027,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>206046</v>
+        <v>100048</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Älg</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alces alces</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1049,26 +1044,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kungagraven, Vg</t>
+          <t>Rapungaberget, Rapungaberget, Vg</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>337416</v>
+        <v>337503</v>
       </c>
       <c r="R5" t="n">
-        <v>6434858</v>
+        <v>6434789</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1095,22 +1081,27 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Födosökande på grenar av äldre gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1125,16 +1116,137 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Mats Eriksson</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Mats Eriksson</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137054794</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>137095159</v>
+      </c>
+      <c r="B6" t="n">
+        <v>56739</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>206046</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Älg</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Alces alces</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Kungagraven, Vg</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>337416</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6434858</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>09:56</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>09:56</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Mats Eriksson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Mats Eriksson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/137095159</t>
         </is>
@@ -1146,6 +1258,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 40629-2026 artfynd.xlsx
+++ b/artfynd/A 40629-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137168521</v>
       </c>
       <c r="B2" t="n">
-        <v>96957</v>
+        <v>96959</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137054854</v>
       </c>
       <c r="B3" t="n">
-        <v>96584</v>
+        <v>96586</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 40629-2026 artfynd.xlsx
+++ b/artfynd/A 40629-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137168521</v>
       </c>
       <c r="B2" t="n">
-        <v>96959</v>
+        <v>96961</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137054854</v>
       </c>
       <c r="B3" t="n">
-        <v>96586</v>
+        <v>96588</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137058376</v>
       </c>
       <c r="B4" t="n">
-        <v>92806</v>
+        <v>92808</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 40629-2026 artfynd.xlsx
+++ b/artfynd/A 40629-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137168521</v>
       </c>
       <c r="B2" t="n">
-        <v>96961</v>
+        <v>96974</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137054854</v>
       </c>
       <c r="B3" t="n">
-        <v>96588</v>
+        <v>96601</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137058376</v>
       </c>
       <c r="B4" t="n">
-        <v>92808</v>
+        <v>92821</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137054794</v>
       </c>
       <c r="B5" t="n">
-        <v>58021</v>
+        <v>58034</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>137095159</v>
       </c>
       <c r="B6" t="n">
-        <v>56739</v>
+        <v>56752</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 40629-2026 artfynd.xlsx
+++ b/artfynd/A 40629-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137168521</v>
       </c>
       <c r="B2" t="n">
-        <v>96974</v>
+        <v>96976</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137054854</v>
       </c>
       <c r="B3" t="n">
-        <v>96601</v>
+        <v>96603</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137058376</v>
       </c>
       <c r="B4" t="n">
-        <v>92821</v>
+        <v>92823</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137054794</v>
       </c>
       <c r="B5" t="n">
-        <v>58034</v>
+        <v>58036</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>137095159</v>
       </c>
       <c r="B6" t="n">
-        <v>56752</v>
+        <v>56754</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 40629-2026 artfynd.xlsx
+++ b/artfynd/A 40629-2026 artfynd.xlsx
@@ -1166,11 +1166,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Kungagraven, Vg</t>

--- a/artfynd/A 40629-2026 artfynd.xlsx
+++ b/artfynd/A 40629-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137168521</v>
       </c>
       <c r="B2" t="n">
-        <v>96976</v>
+        <v>96979</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137054854</v>
       </c>
       <c r="B3" t="n">
-        <v>96603</v>
+        <v>96606</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137058376</v>
       </c>
       <c r="B4" t="n">
-        <v>92823</v>
+        <v>92826</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 40629-2026 artfynd.xlsx
+++ b/artfynd/A 40629-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137168521</v>
       </c>
       <c r="B2" t="n">
-        <v>96979</v>
+        <v>96989</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137054854</v>
       </c>
       <c r="B3" t="n">
-        <v>96606</v>
+        <v>96616</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137058376</v>
       </c>
       <c r="B4" t="n">
-        <v>92826</v>
+        <v>92836</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137054794</v>
       </c>
       <c r="B5" t="n">
-        <v>58036</v>
+        <v>58046</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>137095159</v>
       </c>
       <c r="B6" t="n">
-        <v>56754</v>
+        <v>56764</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 40629-2026 artfynd.xlsx
+++ b/artfynd/A 40629-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137168521</v>
       </c>
       <c r="B2" t="n">
-        <v>96989</v>
+        <v>96990</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137054854</v>
       </c>
       <c r="B3" t="n">
-        <v>96616</v>
+        <v>96617</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137058376</v>
       </c>
       <c r="B4" t="n">
-        <v>92836</v>
+        <v>92837</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 40629-2026 artfynd.xlsx
+++ b/artfynd/A 40629-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137168521</v>
       </c>
       <c r="B2" t="n">
-        <v>96990</v>
+        <v>96995</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137054854</v>
       </c>
       <c r="B3" t="n">
-        <v>96617</v>
+        <v>96622</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137058376</v>
       </c>
       <c r="B4" t="n">
-        <v>92837</v>
+        <v>92840</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137054794</v>
       </c>
       <c r="B5" t="n">
-        <v>58046</v>
+        <v>58047</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>137095159</v>
       </c>
       <c r="B6" t="n">
-        <v>56764</v>
+        <v>56765</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 40629-2026 artfynd.xlsx
+++ b/artfynd/A 40629-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137168521</v>
       </c>
       <c r="B2" t="n">
-        <v>96995</v>
+        <v>96997</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137054854</v>
       </c>
       <c r="B3" t="n">
-        <v>96622</v>
+        <v>96624</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137058376</v>
       </c>
       <c r="B4" t="n">
-        <v>92840</v>
+        <v>92842</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 40629-2026 artfynd.xlsx
+++ b/artfynd/A 40629-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137168521</v>
       </c>
       <c r="B2" t="n">
-        <v>96997</v>
+        <v>97003</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137054854</v>
       </c>
       <c r="B3" t="n">
-        <v>96624</v>
+        <v>96630</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137058376</v>
       </c>
       <c r="B4" t="n">
-        <v>92842</v>
+        <v>92847</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137054794</v>
       </c>
       <c r="B5" t="n">
-        <v>58047</v>
+        <v>58048</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 40629-2026 artfynd.xlsx
+++ b/artfynd/A 40629-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137168521</v>
       </c>
       <c r="B2" t="n">
-        <v>97003</v>
+        <v>97015</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137054854</v>
       </c>
       <c r="B3" t="n">
-        <v>96630</v>
+        <v>96642</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137058376</v>
       </c>
       <c r="B4" t="n">
-        <v>92847</v>
+        <v>92859</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1045,6 +1045,10 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Rapungaberget, Rapungaberget, Vg</t>

--- a/artfynd/A 40629-2026 artfynd.xlsx
+++ b/artfynd/A 40629-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137168521</v>
       </c>
       <c r="B2" t="n">
-        <v>97015</v>
+        <v>97016</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137054854</v>
       </c>
       <c r="B3" t="n">
-        <v>96642</v>
+        <v>96643</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137058376</v>
       </c>
       <c r="B4" t="n">
-        <v>92859</v>
+        <v>92860</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 40629-2026 artfynd.xlsx
+++ b/artfynd/A 40629-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137168521</v>
       </c>
       <c r="B2" t="n">
-        <v>97016</v>
+        <v>97019</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137054854</v>
       </c>
       <c r="B3" t="n">
-        <v>96643</v>
+        <v>96646</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137058376</v>
       </c>
       <c r="B4" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 40629-2026 artfynd.xlsx
+++ b/artfynd/A 40629-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137168521</v>
       </c>
       <c r="B2" t="n">
-        <v>97019</v>
+        <v>97023</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137054854</v>
       </c>
       <c r="B3" t="n">
-        <v>96646</v>
+        <v>96650</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137058376</v>
       </c>
       <c r="B4" t="n">
-        <v>92863</v>
+        <v>92867</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137054794</v>
       </c>
       <c r="B5" t="n">
-        <v>58048</v>
+        <v>58051</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         <v>137095159</v>
       </c>
       <c r="B6" t="n">
-        <v>56765</v>
+        <v>56768</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
